--- a/data/trans_dic/P2C_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
+          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31,13; 40,88</t>
+          <t>31,2; 40,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>40,99; 50,2</t>
+          <t>40,95; 50,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,47; 50,83</t>
+          <t>40,71; 50,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,51; 11,02</t>
+          <t>6,63; 11,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>42,49; 51,1</t>
+          <t>41,82; 50,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,95; 63,48</t>
+          <t>54,49; 63,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,5; 50,73</t>
+          <t>41,06; 50,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,33; 13,22</t>
+          <t>8,42; 13,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>38,66; 44,87</t>
+          <t>38,37; 44,67</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49,2; 56,01</t>
+          <t>49,43; 56,04</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42,5; 49,62</t>
+          <t>42,34; 49,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,06; 11,51</t>
+          <t>8,13; 11,57</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,43; 41,84</t>
+          <t>33,75; 41,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45,41; 53,12</t>
+          <t>45,41; 53,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41,52; 49,71</t>
+          <t>41,17; 49,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 11,38</t>
+          <t>4,2; 11,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,55; 52,69</t>
+          <t>44,61; 52,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,81; 65,86</t>
+          <t>58,56; 65,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,47; 58,91</t>
+          <t>51,17; 58,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,93; 18,82</t>
+          <t>14,81; 18,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>40,69; 46,39</t>
+          <t>40,69; 46,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53,4; 58,72</t>
+          <t>53,4; 59,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48,06; 53,82</t>
+          <t>47,95; 53,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,23; 14,12</t>
+          <t>8,27; 14,19</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,41; 41,44</t>
+          <t>31,4; 41,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46,14; 56,13</t>
+          <t>46,59; 56,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41,07; 50,42</t>
+          <t>40,77; 50,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 9,1</t>
+          <t>4,54; 8,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39,24; 47,96</t>
+          <t>39,18; 48,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,86; 71,73</t>
+          <t>63,21; 71,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,07; 59,08</t>
+          <t>50,21; 59,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,05; 59,99</t>
+          <t>10,07; 64,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37,0; 43,5</t>
+          <t>36,81; 43,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56,62; 63,35</t>
+          <t>56,69; 63,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47,37; 54,29</t>
+          <t>47,12; 53,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,29; 46,04</t>
+          <t>8,17; 45,75</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,35; 41,72</t>
+          <t>33,62; 41,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46,17; 54,98</t>
+          <t>46,26; 55,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,1; 44,86</t>
+          <t>36,61; 44,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,83; 9,05</t>
+          <t>5,95; 9,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>40,76; 48,61</t>
+          <t>41,0; 48,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,8; 62,52</t>
+          <t>54,7; 62,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,99; 52,12</t>
+          <t>44,01; 52,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,66; 10,15</t>
+          <t>6,44; 9,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,71; 44,32</t>
+          <t>39,03; 44,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52,62; 58,11</t>
+          <t>52,61; 57,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41,9; 47,38</t>
+          <t>41,66; 47,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,78; 9,12</t>
+          <t>6,8; 9,23</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,72; 39,18</t>
+          <t>34,87; 39,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>47,11; 51,56</t>
+          <t>47,11; 51,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41,86; 46,42</t>
+          <t>42,06; 46,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,1; 8,84</t>
+          <t>6,04; 8,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>43,93; 47,96</t>
+          <t>44,12; 48,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,71; 63,48</t>
+          <t>59,51; 63,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,92; 53,39</t>
+          <t>49,1; 53,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,42; 32,69</t>
+          <t>11,38; 32,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>40,34; 43,43</t>
+          <t>40,34; 43,48</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54,38; 57,44</t>
+          <t>54,27; 57,27</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46,46; 49,6</t>
+          <t>46,32; 49,57</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,46; 21,65</t>
+          <t>9,45; 20,25</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
+          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>131725; 172959</t>
+          <t>131989; 173373</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>193670; 237221</t>
+          <t>193495; 239360</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>161072; 202293</t>
+          <t>162018; 199174</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41336; 69996</t>
+          <t>42104; 70567</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>209090; 251441</t>
+          <t>205756; 250742</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>282762; 326671</t>
+          <t>280389; 327196</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>185292; 226500</t>
+          <t>183300; 226235</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>60448; 95913</t>
+          <t>61058; 94740</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>353804; 410585</t>
+          <t>351162; 408771</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>485697; 552915</t>
+          <t>487913; 553151</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>358917; 418968</t>
+          <t>357545; 415194</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>109744; 156667</t>
+          <t>110575; 157466</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>196051; 245398</t>
+          <t>197941; 245306</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>300398; 351412</t>
+          <t>300386; 351738</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>241811; 289473</t>
+          <t>239725; 289806</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50134; 135755</t>
+          <t>50137; 133847</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>289667; 342601</t>
+          <t>290036; 341204</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>439255; 491903</t>
+          <t>437349; 492260</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>369075; 422394</t>
+          <t>366931; 420622</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>143150; 180456</t>
+          <t>141958; 181925</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>503204; 573735</t>
+          <t>503236; 573519</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>752135; 827006</t>
+          <t>752010; 832552</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>624455; 699342</t>
+          <t>623101; 697610</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>177066; 303830</t>
+          <t>177933; 305202</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>126720; 167144</t>
+          <t>126649; 166261</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>210975; 256648</t>
+          <t>213044; 256978</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>170914; 209844</t>
+          <t>169648; 211186</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32537; 64158</t>
+          <t>31975; 60708</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>186830; 228326</t>
+          <t>186538; 229750</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>334263; 381412</t>
+          <t>336093; 378903</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>256991; 303268</t>
+          <t>257716; 303978</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>93805; 559972</t>
+          <t>93984; 602595</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>325415; 382543</t>
+          <t>323772; 380744</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>559916; 626522</t>
+          <t>560625; 627684</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>440276; 504640</t>
+          <t>438012; 501479</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>135752; 754224</t>
+          <t>133852; 749377</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>165839; 207465</t>
+          <t>167158; 208360</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>252134; 300236</t>
+          <t>252581; 301997</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>180694; 224502</t>
+          <t>183233; 223696</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54078; 83878</t>
+          <t>55103; 87531</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>278412; 332050</t>
+          <t>280085; 329656</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>396537; 452435</t>
+          <t>395872; 449695</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>289548; 343070</t>
+          <t>289700; 343616</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>72873; 111174</t>
+          <t>70543; 108859</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>456836; 523075</t>
+          <t>460720; 525330</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>668092; 737852</t>
+          <t>667988; 735175</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>485520; 549041</t>
+          <t>482720; 553888</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>137037; 184424</t>
+          <t>137504; 186512</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>663183; 748468</t>
+          <t>666019; 749273</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1006826; 1101905</t>
+          <t>1006836; 1105466</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>794075; 880538</t>
+          <t>797796; 881605</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>211217; 305947</t>
+          <t>209116; 305479</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1010970; 1103813</t>
+          <t>1015276; 1109391</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1502778; 1597594</t>
+          <t>1497883; 1594913</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1142237; 1246758</t>
+          <t>1146440; 1247762</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>423866; 1213729</t>
+          <t>422326; 1190097</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1698885; 1829024</t>
+          <t>1698777; 1830993</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2530825; 2673145</t>
+          <t>2525671; 2665308</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1966355; 2099250</t>
+          <t>1960395; 2097694</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>678344; 1552438</t>
+          <t>678095; 1452481</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31,2; 40,98</t>
+          <t>31,27; 40,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>40,95; 50,66</t>
+          <t>41,01; 50,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,71; 50,05</t>
+          <t>39,93; 50,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,63; 11,11</t>
+          <t>6,6; 11,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>41,82; 50,96</t>
+          <t>42,46; 51,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,49; 63,58</t>
+          <t>54,58; 63,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,06; 50,67</t>
+          <t>41,62; 50,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,42; 13,06</t>
+          <t>9,98; 14,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>38,37; 44,67</t>
+          <t>38,59; 44,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49,43; 56,04</t>
+          <t>49,01; 55,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42,34; 49,17</t>
+          <t>42,38; 49,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,13; 11,57</t>
+          <t>8,89; 11,99</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,75; 41,82</t>
+          <t>33,88; 41,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45,41; 53,17</t>
+          <t>45,38; 53,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41,17; 49,77</t>
+          <t>41,22; 49,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 11,22</t>
+          <t>9,72; 14,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,61; 52,48</t>
+          <t>44,57; 52,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,56; 65,91</t>
+          <t>58,72; 66,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,17; 58,66</t>
+          <t>51,11; 58,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,81; 18,98</t>
+          <t>15,21; 19,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>40,69; 46,38</t>
+          <t>40,72; 46,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53,4; 59,11</t>
+          <t>53,64; 59,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47,95; 53,69</t>
+          <t>48,23; 53,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,27; 14,19</t>
+          <t>12,84; 15,92</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,4; 41,22</t>
+          <t>31,23; 40,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46,59; 56,2</t>
+          <t>46,71; 56,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40,77; 50,75</t>
+          <t>40,99; 50,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,54; 8,61</t>
+          <t>4,87; 9,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39,18; 48,26</t>
+          <t>39,41; 48,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63,21; 71,26</t>
+          <t>62,71; 71,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,21; 59,22</t>
+          <t>50,17; 58,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,07; 64,56</t>
+          <t>9,93; 14,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,81; 43,29</t>
+          <t>36,7; 43,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56,69; 63,47</t>
+          <t>56,56; 63,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47,12; 53,95</t>
+          <t>47,17; 54,14</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,17; 45,75</t>
+          <t>7,79; 10,9</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,62; 41,9</t>
+          <t>33,19; 41,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46,26; 55,31</t>
+          <t>46,49; 55,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,61; 44,7</t>
+          <t>36,06; 44,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,95; 9,44</t>
+          <t>6,26; 9,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,0; 48,26</t>
+          <t>40,64; 48,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,7; 62,14</t>
+          <t>54,39; 61,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,01; 52,2</t>
+          <t>44,22; 52,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,44; 9,94</t>
+          <t>8,56; 11,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39,03; 44,51</t>
+          <t>38,89; 44,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52,61; 57,9</t>
+          <t>52,39; 58,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41,66; 47,8</t>
+          <t>41,84; 47,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,8; 9,23</t>
+          <t>7,86; 10,07</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,87; 39,22</t>
+          <t>34,77; 39,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>47,11; 51,72</t>
+          <t>47,28; 51,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42,06; 46,48</t>
+          <t>42,21; 46,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,04; 8,83</t>
+          <t>7,94; 9,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>44,12; 48,21</t>
+          <t>44,09; 48,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,51; 63,37</t>
+          <t>59,67; 63,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,1; 53,44</t>
+          <t>49,18; 53,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,38; 32,06</t>
+          <t>11,77; 13,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>40,34; 43,48</t>
+          <t>40,25; 43,36</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54,27; 57,27</t>
+          <t>54,48; 57,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46,32; 49,57</t>
+          <t>46,66; 49,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,45; 20,25</t>
+          <t>10,22; 11,69</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54926</t>
+          <t>59739</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>78672</t>
+          <t>87139</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>133598</t>
+          <t>146878</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>131989; 173373</t>
+          <t>132325; 172133</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>193495; 239360</t>
+          <t>193756; 236372</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>162018; 199174</t>
+          <t>158888; 199955</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42104; 70567</t>
+          <t>45587; 78082</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>205756; 250742</t>
+          <t>208927; 251502</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>280389; 327196</t>
+          <t>280885; 325467</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>183300; 226235</t>
+          <t>185819; 227261</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>61058; 94740</t>
+          <t>73247; 105910</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>351162; 408771</t>
+          <t>353145; 411247</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>487913; 553151</t>
+          <t>483795; 549387</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>357545; 415194</t>
+          <t>357890; 415401</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>110575; 157466</t>
+          <t>126685; 170838</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100174</t>
+          <t>123280</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>161039</t>
+          <t>184020</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>261213</t>
+          <t>307301</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>197941; 245306</t>
+          <t>198694; 245690</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>300386; 351738</t>
+          <t>300235; 351945</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>239725; 289806</t>
+          <t>240056; 290447</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50137; 133847</t>
+          <t>101920; 148634</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>290036; 341204</t>
+          <t>289755; 341563</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>437349; 492260</t>
+          <t>438556; 494577</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>366931; 420622</t>
+          <t>366477; 422122</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>141958; 181925</t>
+          <t>162989; 207965</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>503236; 573519</t>
+          <t>503625; 577258</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>752010; 832552</t>
+          <t>755474; 832374</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>623101; 697610</t>
+          <t>626671; 696056</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>177933; 305202</t>
+          <t>272206; 337647</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44333</t>
+          <t>52912</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>284333</t>
+          <t>97935</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>328665</t>
+          <t>150846</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>126649; 166261</t>
+          <t>125994; 164014</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>213044; 256978</t>
+          <t>213574; 258411</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>169648; 211186</t>
+          <t>170570; 211710</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31975; 60708</t>
+          <t>39115; 73207</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>186538; 229750</t>
+          <t>187639; 231182</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>336093; 378903</t>
+          <t>333458; 381121</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>257716; 303978</t>
+          <t>257510; 302007</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>93984; 602595</t>
+          <t>80679; 116065</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>323772; 380744</t>
+          <t>322781; 382026</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>560625; 627684</t>
+          <t>559304; 624326</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>438012; 501479</t>
+          <t>438471; 503174</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>133852; 749377</t>
+          <t>125795; 176089</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68083</t>
+          <t>77309</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>93131</t>
+          <t>111544</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>161214</t>
+          <t>188854</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>167158; 208360</t>
+          <t>165049; 207666</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>252581; 301997</t>
+          <t>253877; 302531</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>183233; 223696</t>
+          <t>180470; 222897</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55103; 87531</t>
+          <t>61959; 96042</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>280085; 329656</t>
+          <t>277610; 330091</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>395872; 449695</t>
+          <t>393574; 447985</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>289700; 343616</t>
+          <t>291079; 344016</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>70543; 108859</t>
+          <t>95836; 131676</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>460720; 525330</t>
+          <t>459063; 523723</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>667988; 735175</t>
+          <t>665159; 737991</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>482720; 553888</t>
+          <t>484825; 553166</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>137504; 186512</t>
+          <t>165691; 212412</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>267516</t>
+          <t>313239</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>617174</t>
+          <t>480638</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>884690</t>
+          <t>793878</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>666019; 749273</t>
+          <t>664139; 750667</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1006836; 1105466</t>
+          <t>1010607; 1101968</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>797796; 881605</t>
+          <t>800754; 881590</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>209116; 305479</t>
+          <t>280385; 350896</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1015276; 1109391</t>
+          <t>1014719; 1108578</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1497883; 1594913</t>
+          <t>1501790; 1599144</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1146440; 1247762</t>
+          <t>1148280; 1246540</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>422326; 1190097</t>
+          <t>439680; 517265</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1698777; 1830993</t>
+          <t>1695103; 1826314</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2525671; 2665308</t>
+          <t>2535549; 2675987</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1960395; 2097694</t>
+          <t>1974561; 2109294</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>678095; 1452481</t>
+          <t>743311; 849666</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
